--- a/output/tables/2025/tabla4_clusters.xlsx
+++ b/output/tables/2025/tabla4_clusters.xlsx
@@ -604,64 +604,72 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>2798264</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="2" t="n">
         <v>23.36</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="2" t="n">
         <v>23.36</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="2" t="n">
         <v>100</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2331401</v>
+      </c>
+      <c r="E8" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="F8" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19.46</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>2331401</v>
+        <v>1825777</v>
       </c>
       <c r="E9" t="n">
-        <v>19.46</v>
+        <v>15.24</v>
       </c>
       <c r="F9" t="n">
-        <v>19.46</v>
+        <v>15.24</v>
       </c>
       <c r="G9" t="n">
-        <v>19.46</v>
+        <v>34.71</v>
       </c>
     </row>
     <row r="10">
@@ -669,22 +677,22 @@
         <v>19</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>1825777</v>
+        <v>2477427</v>
       </c>
       <c r="E10" t="n">
-        <v>15.24</v>
+        <v>20.68</v>
       </c>
       <c r="F10" t="n">
-        <v>15.24</v>
+        <v>20.68</v>
       </c>
       <c r="G10" t="n">
-        <v>34.71</v>
+        <v>55.39</v>
       </c>
     </row>
     <row r="11">
@@ -692,106 +700,114 @@
         <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>2477427</v>
+        <v>2545515</v>
       </c>
       <c r="E11" t="n">
-        <v>20.68</v>
+        <v>21.25</v>
       </c>
       <c r="F11" t="n">
-        <v>20.68</v>
+        <v>21.25</v>
       </c>
       <c r="G11" t="n">
-        <v>55.39</v>
+        <v>76.64</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2545515</v>
-      </c>
-      <c r="E12" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="F12" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="G12" t="n">
-        <v>76.64</v>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2798264</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>2798264</v>
+        <v>2331401</v>
       </c>
       <c r="E13" t="n">
-        <v>23.36</v>
+        <v>19.46</v>
       </c>
       <c r="F13" t="n">
-        <v>23.36</v>
+        <v>19.46</v>
       </c>
       <c r="G13" t="n">
-        <v>100</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1825777</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15.24</v>
+      </c>
+      <c r="G14" t="n">
+        <v>34.71</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>2331401</v>
+        <v>2477427</v>
       </c>
       <c r="E15" t="n">
-        <v>19.46</v>
+        <v>20.68</v>
       </c>
       <c r="F15" t="n">
-        <v>19.46</v>
+        <v>20.68</v>
       </c>
       <c r="G15" t="n">
-        <v>19.46</v>
+        <v>55.39</v>
       </c>
     </row>
     <row r="16">
@@ -799,84 +815,23 @@
         <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>1825777</v>
+        <v>5343779</v>
       </c>
       <c r="E16" t="n">
-        <v>15.24</v>
+        <v>44.61</v>
       </c>
       <c r="F16" t="n">
-        <v>15.24</v>
+        <v>44.61</v>
       </c>
       <c r="G16" t="n">
-        <v>34.71</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2477427</v>
-      </c>
-      <c r="E17" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="F17" t="n">
-        <v>20.68</v>
-      </c>
-      <c r="G17" t="n">
-        <v>55.39</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" t="n">
-        <v>5343779</v>
-      </c>
-      <c r="E18" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="F18" t="n">
-        <v>44.61</v>
-      </c>
-      <c r="G18" t="n">
         <v>100</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19"/>
-      <c r="G19"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>

--- a/output/tables/2025/tabla4_clusters.xlsx
+++ b/output/tables/2025/tabla4_clusters.xlsx
@@ -499,16 +499,16 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>1101373</v>
+        <v>2503950</v>
       </c>
       <c r="E2" t="n">
-        <v>9.19</v>
+        <v>20.9</v>
       </c>
       <c r="F2" t="n">
-        <v>9.19</v>
+        <v>20.9</v>
       </c>
       <c r="G2" t="n">
-        <v>9.19</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="3">
@@ -522,16 +522,16 @@
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>1230028</v>
+        <v>670155</v>
       </c>
       <c r="E3" t="n">
-        <v>10.27</v>
+        <v>5.59</v>
       </c>
       <c r="F3" t="n">
-        <v>10.27</v>
+        <v>5.59</v>
       </c>
       <c r="G3" t="n">
-        <v>19.46</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="4">
@@ -545,16 +545,16 @@
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>1825777</v>
+        <v>1518261</v>
       </c>
       <c r="E4" t="n">
-        <v>15.24</v>
+        <v>12.68</v>
       </c>
       <c r="F4" t="n">
-        <v>15.24</v>
+        <v>12.68</v>
       </c>
       <c r="G4" t="n">
-        <v>34.71</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="5">
@@ -568,16 +568,16 @@
         <v>13</v>
       </c>
       <c r="D5" t="n">
-        <v>2477427</v>
+        <v>2813680</v>
       </c>
       <c r="E5" t="n">
-        <v>20.68</v>
+        <v>23.49</v>
       </c>
       <c r="F5" t="n">
-        <v>20.68</v>
+        <v>23.49</v>
       </c>
       <c r="G5" t="n">
-        <v>55.39</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="6">
@@ -591,16 +591,16 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>2545515</v>
+        <v>1917832</v>
       </c>
       <c r="E6" t="n">
-        <v>21.25</v>
+        <v>16.01</v>
       </c>
       <c r="F6" t="n">
-        <v>21.25</v>
+        <v>16.01</v>
       </c>
       <c r="G6" t="n">
-        <v>76.64</v>
+        <v>78.67</v>
       </c>
     </row>
     <row r="7">
@@ -614,13 +614,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2798264</v>
+        <v>2554506</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>23.36</v>
+        <v>21.33</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>23.36</v>
+        <v>21.33</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>100</v>
@@ -637,16 +637,16 @@
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>2331401</v>
+        <v>2503950</v>
       </c>
       <c r="E8" t="n">
-        <v>19.46</v>
+        <v>20.9</v>
       </c>
       <c r="F8" t="n">
-        <v>19.46</v>
+        <v>20.9</v>
       </c>
       <c r="G8" t="n">
-        <v>19.46</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="9">
@@ -660,16 +660,16 @@
         <v>13</v>
       </c>
       <c r="D9" t="n">
-        <v>1825777</v>
+        <v>670155</v>
       </c>
       <c r="E9" t="n">
-        <v>15.24</v>
+        <v>5.59</v>
       </c>
       <c r="F9" t="n">
-        <v>15.24</v>
+        <v>5.59</v>
       </c>
       <c r="G9" t="n">
-        <v>34.71</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="10">
@@ -683,16 +683,16 @@
         <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>2477427</v>
+        <v>4331941</v>
       </c>
       <c r="E10" t="n">
-        <v>20.68</v>
+        <v>36.16</v>
       </c>
       <c r="F10" t="n">
-        <v>20.68</v>
+        <v>36.16</v>
       </c>
       <c r="G10" t="n">
-        <v>55.39</v>
+        <v>62.66</v>
       </c>
     </row>
     <row r="11">
@@ -706,16 +706,16 @@
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>2545515</v>
+        <v>1917832</v>
       </c>
       <c r="E11" t="n">
-        <v>21.25</v>
+        <v>16.01</v>
       </c>
       <c r="F11" t="n">
-        <v>21.25</v>
+        <v>16.01</v>
       </c>
       <c r="G11" t="n">
-        <v>76.64</v>
+        <v>78.67</v>
       </c>
     </row>
     <row r="12">
@@ -729,13 +729,13 @@
         <v>13</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2798264</v>
+        <v>2554506</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>23.36</v>
+        <v>21.33</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>23.36</v>
+        <v>21.33</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>100</v>
@@ -752,16 +752,16 @@
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>2331401</v>
+        <v>2503950</v>
       </c>
       <c r="E13" t="n">
-        <v>19.46</v>
+        <v>20.9</v>
       </c>
       <c r="F13" t="n">
-        <v>19.46</v>
+        <v>20.9</v>
       </c>
       <c r="G13" t="n">
-        <v>19.46</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="14">
@@ -775,16 +775,16 @@
         <v>13</v>
       </c>
       <c r="D14" t="n">
-        <v>1825777</v>
+        <v>670155</v>
       </c>
       <c r="E14" t="n">
-        <v>15.24</v>
+        <v>5.59</v>
       </c>
       <c r="F14" t="n">
-        <v>15.24</v>
+        <v>5.59</v>
       </c>
       <c r="G14" t="n">
-        <v>34.71</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="15">
@@ -798,16 +798,16 @@
         <v>13</v>
       </c>
       <c r="D15" t="n">
-        <v>2477427</v>
+        <v>6249773</v>
       </c>
       <c r="E15" t="n">
-        <v>20.68</v>
+        <v>52.18</v>
       </c>
       <c r="F15" t="n">
-        <v>20.68</v>
+        <v>52.18</v>
       </c>
       <c r="G15" t="n">
-        <v>55.39</v>
+        <v>78.67</v>
       </c>
     </row>
     <row r="16">
@@ -821,13 +821,13 @@
         <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>5343779</v>
+        <v>2554506</v>
       </c>
       <c r="E16" t="n">
-        <v>44.61</v>
+        <v>21.33</v>
       </c>
       <c r="F16" t="n">
-        <v>44.61</v>
+        <v>21.33</v>
       </c>
       <c r="G16" t="n">
         <v>100</v>

--- a/output/tables/2025/tabla4_clusters.xlsx
+++ b/output/tables/2025/tabla4_clusters.xlsx
@@ -6,26 +6,13 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="AVISO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="clusters" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="clusters" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t xml:space="preserve">aviso</t>
-  </si>
-  <si>
-    <t xml:space="preserve">motivo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PROVISIONAL - no citar como número final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D2 abierta (PLAN.md): la solución de cluster depende de la categorización que entra al MCA.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t xml:space="preserve">variable</t>
   </si>
@@ -428,33 +415,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="10.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="3.71" hidden="0" customWidth="1"/>
@@ -467,36 +427,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>2503950</v>
@@ -513,13 +473,13 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>670155</v>
@@ -536,13 +496,13 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>1518261</v>
@@ -559,13 +519,13 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>2813680</v>
@@ -582,13 +542,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>1917832</v>
@@ -605,13 +565,13 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2554506</v>
@@ -628,13 +588,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>2503950</v>
@@ -651,13 +611,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>670155</v>
@@ -674,13 +634,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>4331941</v>
@@ -697,13 +657,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>1917832</v>
@@ -720,13 +680,13 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2554506</v>
@@ -743,13 +703,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>2503950</v>
@@ -766,13 +726,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>670155</v>
@@ -789,13 +749,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>6249773</v>
@@ -812,13 +772,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>2554506</v>
